--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_233_R24.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_233_R24.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.868</v>
+        <v>7.3232</v>
       </c>
       <c r="E2" t="n">
-        <v>5.304</v>
+        <v>6.3223</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5639999999999999</v>
+        <v>1.0009</v>
       </c>
       <c r="G2" t="n">
         <v>9.7281</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.9323</v>
+        <v>-1.4771</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3364</v>
+        <v>-0.3181</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.596</v>
+        <v>-1.1591</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6331</v>
+        <v>0.6469</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2511</v>
+        <v>-1.0021</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8842</v>
+        <v>1.649</v>
       </c>
       <c r="G3" t="n">
         <v>-2.5375</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4747</v>
+        <v>0.4885</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3961</v>
+        <v>0.6451</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0786</v>
+        <v>-0.1566</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. HOARD</t>
+          <t>I. LUNDBERG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6145</v>
+        <v>0.2699</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0021</v>
+        <v>0.72</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3876</v>
+        <v>-0.4502</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1436</v>
+        <v>0.2353</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8631</v>
+        <v>1.808</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7195</v>
+        <v>-1.5727</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2288</v>
+        <v>0.3823</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.376</v>
+        <v>2.4738</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472</v>
+        <v>-2.0915</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0853</v>
+        <v>-0.1471</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.487</v>
+        <v>-0.6659</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5723</v>
+        <v>0.5188</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R4" t="n">
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5983000000000001</v>
+        <v>-1.0222</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4629</v>
+        <v>0.2087</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8645</v>
+        <v>-1.2309</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5361</v>
+        <v>2.6805</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.6805</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. SORKIN</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5513</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6688</v>
+        <v>-2.2651</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1175</v>
+        <v>2.182</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5861</v>
+        <v>-1.3441</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.131</v>
+        <v>-0.1094</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4551</v>
+        <v>-1.2347</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1887</v>
+        <v>-2.4201</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3669</v>
+        <v>-0.2451</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5556</v>
+        <v>-2.175</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3973</v>
+        <v>1.0761</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4978</v>
+        <v>0.1357</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1005</v>
+        <v>0.9403</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6012</v>
+        <v>-0.1513</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2492</v>
+        <v>-0.3811</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.648</v>
+        <v>0.2298</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.2525</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>J. HOARD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2035</v>
+        <v>-0.1529</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9113</v>
+        <v>0.369</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1148</v>
+        <v>-0.522</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3441</v>
+        <v>-0.1436</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1094</v>
+        <v>-0.8631</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2347</v>
+        <v>0.7195</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.4201</v>
+        <v>-0.2288</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2451</v>
+        <v>-0.376</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.175</v>
+        <v>0.1472</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0761</v>
+        <v>0.0853</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1357</v>
+        <v>-0.487</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9403</v>
+        <v>0.5723</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1353</v>
+        <v>-0.1691</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0272</v>
+        <v>0.8298</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1625</v>
+        <v>-0.999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2525</v>
+        <v>-0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2836</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7297</v>
+        <v>-0.6796</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0168</v>
+        <v>0.1848</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3775</v>
@@ -1000,13 +1000,13 @@
         <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6743</v>
+        <v>-0.6242</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9379</v>
+        <v>-0.7699</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. LEAF</t>
+          <t>J. DOWTIN JR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9293</v>
+        <v>-0.8535</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7466</v>
+        <v>-1.7195</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8174</v>
+        <v>0.866</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6944</v>
+        <v>-1.685</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3469</v>
+        <v>-0.1525</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6526</v>
+        <v>-1.5325</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7837</v>
+        <v>-1.3884</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9677</v>
+        <v>0.0371</v>
       </c>
       <c r="L8" t="n">
-        <v>0.184</v>
+        <v>-1.4255</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0893</v>
+        <v>-0.2966</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3792</v>
+        <v>-0.1896</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4685</v>
+        <v>-0.107</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3224</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.963</v>
+        <v>-0.0116</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6405</v>
+        <v>0.0029</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. DOWTIN JR</t>
+          <t>J. CLARK III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1738</v>
+        <v>-0.8631</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0734</v>
+        <v>-0.2963</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8996</v>
+        <v>-0.5668</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.685</v>
+        <v>1.8176</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1525</v>
+        <v>1.9782</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5325</v>
+        <v>-0.1607</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3884</v>
+        <v>1.2564</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0371</v>
+        <v>1.8856</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4255</v>
+        <v>-0.6292</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2966</v>
+        <v>0.5611</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1896</v>
+        <v>0.0926</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.107</v>
+        <v>0.4685</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.329</v>
+        <v>-0.3765</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3655</v>
+        <v>-0.393</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0365</v>
+        <v>0.0165</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0722</v>
+        <v>-1.6083</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. LUNDBERG</t>
+          <t>T. LEAF</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2532</v>
+        <v>-0.9115</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5342</v>
+        <v>-1.3928</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.719</v>
+        <v>0.4813</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2353</v>
+        <v>-0.6944</v>
       </c>
       <c r="H10" t="n">
-        <v>1.808</v>
+        <v>-1.3469</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5727</v>
+        <v>0.6526</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3823</v>
+        <v>-0.7837</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4738</v>
+        <v>-0.9677</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0915</v>
+        <v>0.184</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1471</v>
+        <v>0.0893</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6659</v>
+        <v>-0.3792</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5188</v>
+        <v>0.4685</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.5453</v>
+        <v>-0.3047</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0455</v>
+        <v>-0.6091</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4998</v>
+        <v>0.3044</v>
       </c>
       <c r="V10" t="n">
-        <v>2.6805</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6805</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CLARK III</t>
+          <t>R. SORKIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3849</v>
+        <v>-0.9232</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.6501</v>
+        <v>-0.4361</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7348</v>
+        <v>-0.4871</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8176</v>
+        <v>-0.5861</v>
       </c>
       <c r="H11" t="n">
-        <v>1.9782</v>
+        <v>-0.131</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1607</v>
+        <v>-0.4551</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2564</v>
+        <v>-0.1887</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8856</v>
+        <v>0.3669</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6292</v>
+        <v>-0.5556</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5611</v>
+        <v>-0.3973</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0926</v>
+        <v>-0.4978</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4685</v>
+        <v>0.1005</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8984</v>
+        <v>0.1267</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7468</v>
+        <v>1.1444</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1516</v>
+        <v>-1.0176</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.3995</v>
+        <v>3.7731</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9382999999999996</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="F12" t="n">
         <v>4.337899999999999</v>
@@ -1363,10 +1363,10 @@
         <v>2.894000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0192</v>
+        <v>1.019199999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3293</v>
+        <v>3.329300000000001</v>
       </c>
       <c r="L12" t="n">
         <v>-2.310199999999999</v>
@@ -1384,19 +1384,19 @@
         <v>1.1598</v>
       </c>
       <c r="Q12" t="n">
-        <v>-9.278200000000002</v>
+        <v>-9.2782</v>
       </c>
       <c r="R12" t="n">
         <v>10.4379</v>
       </c>
       <c r="S12" t="n">
-        <v>-3.8922</v>
+        <v>-3.5187</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8874000000000003</v>
+        <v>1.2607</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.7797</v>
+        <v>-4.7795</v>
       </c>
       <c r="V12" t="n">
         <v>1.719</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2403</v>
+        <v>3.6111</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0423</v>
+        <v>3.1551</v>
       </c>
       <c r="F13" t="n">
-        <v>0.198</v>
+        <v>0.456</v>
       </c>
       <c r="G13" t="n">
         <v>0.636</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9806</v>
+        <v>1.3515</v>
       </c>
       <c r="T13" t="n">
-        <v>3.6058</v>
+        <v>1.7185</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6251</v>
+        <v>-0.367</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>T. SHORTS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7532</v>
+        <v>1.9872</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0919</v>
+        <v>1.6109</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6613</v>
+        <v>0.3764</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.7464</v>
+        <v>1.7058</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1776</v>
+        <v>2.3717</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5688</v>
+        <v>-0.6659</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.5782</v>
+        <v>1.3272</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.5441</v>
+        <v>2.6691</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.0341</v>
+        <v>-1.3419</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1682</v>
+        <v>0.3786</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6335</v>
+        <v>-0.2974</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4653</v>
+        <v>0.6761</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>3.644</v>
+        <v>-0.1799</v>
       </c>
       <c r="T14" t="n">
-        <v>2.67</v>
+        <v>0.1419</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9739</v>
+        <v>-0.3218</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.9304</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. SHORTS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6168</v>
+        <v>1.5648</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4314</v>
+        <v>-0.3235</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1855</v>
+        <v>1.8884</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7058</v>
+        <v>-1.7464</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3717</v>
+        <v>-1.1776</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6659</v>
+        <v>-0.5688</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3272</v>
+        <v>-1.5782</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6691</v>
+        <v>-0.5441</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3419</v>
+        <v>-1.0341</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3786</v>
+        <v>-0.1682</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2974</v>
+        <v>-0.6335</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6761</v>
+        <v>0.4653</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5503</v>
+        <v>1.4556</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0376</v>
+        <v>1.2546</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5127</v>
+        <v>0.201</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SAMODUROV</t>
+          <t>V. TOLIOPOULOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2481</v>
+        <v>-0.0814</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1589</v>
+        <v>-0.627</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0892</v>
+        <v>0.5457</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3358</v>
+        <v>-1.3236</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0155</v>
+        <v>-0.5606</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3513</v>
+        <v>-0.763</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3714</v>
+        <v>-1.3809</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0168</v>
+        <v>-0.5175</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3546</v>
+        <v>-0.8635</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0356</v>
+        <v>0.0574</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0323</v>
+        <v>-0.0431</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0033</v>
+        <v>0.1005</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.434</v>
+        <v>0.17</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4876</v>
+        <v>-0.3183</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0536</v>
+        <v>0.4883</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. TOLIOPOULOS</t>
+          <t>A. SAMODUROV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6261</v>
+        <v>-0.2596</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9809</v>
+        <v>-0.3948</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3548</v>
+        <v>0.1353</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3236</v>
+        <v>0.3358</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5606</v>
+        <v>-0.0155</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.763</v>
+        <v>0.3513</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3809</v>
+        <v>0.3714</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5175</v>
+        <v>0.0168</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.8635</v>
+        <v>0.3546</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0574</v>
+        <v>-0.0356</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0431</v>
+        <v>-0.0323</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1005</v>
+        <v>-0.0033</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3747</v>
+        <v>0.4226</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6721</v>
+        <v>0.2517</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2974</v>
+        <v>0.1709</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. KALAITZAKIS</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9054</v>
+        <v>-0.7055</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.92</v>
+        <v>-1.2549</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0145</v>
+        <v>0.5494</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.771</v>
+        <v>0.7883</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0048</v>
+        <v>-0.7876</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7662</v>
+        <v>1.576</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6959</v>
+        <v>0.2632</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0168</v>
+        <v>-0.3221</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7127</v>
+        <v>0.5854</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0751</v>
+        <v>0.5251</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0216</v>
+        <v>-0.4655</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0535</v>
+        <v>0.9906</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1344</v>
+        <v>0.1298</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.224</v>
+        <v>0.8889</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0896</v>
+        <v>-0.7591</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. FARIED</t>
+          <t>P. KALAITZAKIS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6019</v>
+        <v>-0.771</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.92</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7012</v>
+        <v>0.149</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2107</v>
+        <v>-0.771</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1741</v>
+        <v>-0.0048</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3848</v>
+        <v>-0.7662</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5578</v>
+        <v>-0.6959</v>
       </c>
       <c r="K19" t="n">
-        <v>0.521</v>
+        <v>0.0168</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0368</v>
+        <v>-0.7127</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7684</v>
+        <v>-0.0751</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3469</v>
+        <v>-0.0216</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4216</v>
+        <v>-0.0535</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2315</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2987</v>
+        <v>-0.224</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0672</v>
+        <v>0.224</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>N. ROGKAVOPOULOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7341</v>
+        <v>-0.9403</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8943</v>
+        <v>1.5456</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1602</v>
+        <v>-2.4859</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3314</v>
+        <v>-0.1633</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1909</v>
+        <v>0.6665</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1406</v>
+        <v>-0.8298</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5746</v>
+        <v>0.5945</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5377999999999999</v>
+        <v>1.3108</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0368</v>
+        <v>-0.7163</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2431</v>
+        <v>-0.7579</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3469</v>
+        <v>-0.6443</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1038</v>
+        <v>-0.1136</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>0.022</v>
+        <v>0.5298</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1494</v>
+        <v>0.8968</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1713</v>
+        <v>-0.367</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.0026</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>K. FARIED</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7543</v>
+        <v>-1.2652</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6088</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1455</v>
+        <v>-0.6004</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7883</v>
+        <v>-0.2107</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7876</v>
+        <v>0.1741</v>
       </c>
       <c r="I21" t="n">
-        <v>1.576</v>
+        <v>-0.3848</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2632</v>
+        <v>0.5578</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3221</v>
+        <v>0.521</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5854</v>
+        <v>0.0368</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5251</v>
+        <v>-0.7684</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4655</v>
+        <v>-0.3469</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9906</v>
+        <v>-0.4216</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6237</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.919</v>
+        <v>0.1052</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5351</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4541</v>
+        <v>0.168</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. ROGKAVOPOULOS</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3386</v>
+        <v>-1.8014</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2481</v>
+        <v>-1.8943</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5867</v>
+        <v>0.0929</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1633</v>
+        <v>0.3314</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6665</v>
+        <v>0.1909</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8298</v>
+        <v>0.1406</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5945</v>
+        <v>0.5746</v>
       </c>
       <c r="K22" t="n">
-        <v>1.3108</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7163</v>
+        <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7579</v>
+        <v>-0.2431</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6443</v>
+        <v>-0.3469</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1136</v>
+        <v>0.1038</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6959</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8685</v>
+        <v>-0.0452</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4007</v>
+        <v>-0.1494</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4678</v>
+        <v>0.1041</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.0026</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.8012</v>
+        <v>-3.9521</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1518</v>
+        <v>-4.0339</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3506</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-3.9954</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>0.89</v>
+        <v>0.7391</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2636</v>
+        <v>0.3815</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6264</v>
+        <v>0.3576</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.399399999999998</v>
+        <v>-2.6134</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.8017</v>
+        <v>-3.8016</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4022999999999999</v>
+        <v>1.188499999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-4.4131</v>
@@ -2311,13 +2311,13 @@
         <v>-1.0193</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.3293</v>
+        <v>-3.329299999999999</v>
       </c>
       <c r="O24" t="n">
         <v>2.3101</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1599</v>
+        <v>-1.159900000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-10.438</v>
@@ -2326,19 +2326,19 @@
         <v>9.2781</v>
       </c>
       <c r="S24" t="n">
-        <v>3.8922</v>
+        <v>4.678500000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>4.779600000000001</v>
+        <v>4.779399999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8875000000000001</v>
+        <v>-0.101</v>
       </c>
       <c r="V24" t="n">
         <v>-1.719</v>
       </c>
       <c r="W24" t="n">
-        <v>5.250300000000001</v>
+        <v>5.2503</v>
       </c>
       <c r="X24" t="n">
         <v>-6.9693</v>
